--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562667232</v>
+        <v>46157.9307336346</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9307336346</v>
+        <v>46157.93155707599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93155707599</v>
+        <v>46157.93394352425</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394352425</v>
+        <v>46157.93709823046</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709823046</v>
+        <v>46158.28211281575</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211281575</v>
+        <v>46158.29666902207</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666902207</v>
+        <v>46158.29806592401</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806592401</v>
+        <v>46158.33382099279</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382099279</v>
+        <v>46158.36849240706</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36849240706</v>
+        <v>46158.37282232527</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
